--- a/Indicadores/Indicadores-modelo.xlsx
+++ b/Indicadores/Indicadores-modelo.xlsx
@@ -261,7 +261,7 @@
     <t xml:space="preserve">Passo 6</t>
   </si>
   <si>
-    <t xml:space="preserve">Aba Análise: registre a decisão de cada indicador fora da meta, com responsável e prazo.</t>
+    <t xml:space="preserve">Aba Análise: registre a decisão de cada indicador sem atingir a meta, com responsável e prazo.</t>
   </si>
   <si>
     <t xml:space="preserve">Passo 7</t>
@@ -282,7 +282,7 @@
     <t xml:space="preserve">Medições</t>
   </si>
   <si>
-    <t xml:space="preserve">Resultados de cada indicador, em até 12 períodos, e contagem dos períodos seguidos fora da meta.</t>
+    <t xml:space="preserve">Resultados de cada indicador, em até 12 períodos, e contagem dos períodos seguidos sem atingir a meta.</t>
   </si>
   <si>
     <t xml:space="preserve">Painel</t>
@@ -495,7 +495,7 @@
     <t xml:space="preserve">Contagem</t>
   </si>
   <si>
-    <t xml:space="preserve">Períodos seguidos fora da meta</t>
+    <t xml:space="preserve">Períodos seguidos sem atingir a meta</t>
   </si>
   <si>
     <t xml:space="preserve">Contagem calculada a partir dos resultados e da meta de cada indicador. Volta a zero quando o resultado atende à meta.</t>
@@ -519,7 +519,7 @@
     <t xml:space="preserve">Média</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguidos fora da meta</t>
+    <t xml:space="preserve">Seguidos sem atingir a meta</t>
   </si>
   <si>
     <t xml:space="preserve">Média dos 3 anteriores</t>
@@ -549,7 +549,7 @@
     <t xml:space="preserve">Registro das reuniões de análise</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma linha por decisão. Todo indicador fora da meta tem decisão registrada, com responsável e prazo.</t>
+    <t xml:space="preserve">Uma linha por decisão. Todo indicador sem atingir a meta tem decisão registrada, com responsável e prazo.</t>
   </si>
   <si>
     <t xml:space="preserve">Data da reunião</t>
@@ -672,7 +672,7 @@
     <t xml:space="preserve">Os resultados são analisados em reunião, com data marcada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cada indicador fora da meta tem decisão registrada, com responsável e prazo.</t>
+    <t xml:space="preserve">Cada indicador sem atingir a meta tem decisão registrada, com responsável e prazo.</t>
   </si>
   <si>
     <t xml:space="preserve">Os indicadores e as metas são revistos pelo menos uma vez por ano.</t>
@@ -711,7 +711,7 @@
     <t xml:space="preserve">Reunião de análise</t>
   </si>
   <si>
-    <t xml:space="preserve">Toda segunda-feira, com fechamento mensal</t>
+    <t xml:space="preserve">Toda terça-feira, com fechamento mensal</t>
   </si>
   <si>
     <t xml:space="preserve">Situação em</t>
@@ -825,7 +825,7 @@
     <t xml:space="preserve">Set/26</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguidos fora</t>
+    <t xml:space="preserve">Seguidos sem a meta</t>
   </si>
   <si>
     <t xml:space="preserve">Último</t>
@@ -1795,11 +1795,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="12730419"/>
-        <c:axId val="53601548"/>
+        <c:axId val="8375249"/>
+        <c:axId val="97635148"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="12730419"/>
+        <c:axId val="8375249"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1831,7 +1831,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53601548"/>
+        <c:crossAx val="97635148"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1839,7 +1839,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53601548"/>
+        <c:axId val="97635148"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1878,7 +1878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12730419"/>
+        <c:crossAx val="8375249"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2460,11 +2460,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="8494809"/>
-        <c:axId val="72529989"/>
+        <c:axId val="40462582"/>
+        <c:axId val="30770336"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8494809"/>
+        <c:axId val="40462582"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2496,7 +2496,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72529989"/>
+        <c:crossAx val="30770336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2504,7 +2504,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72529989"/>
+        <c:axId val="30770336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2543,7 +2543,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8494809"/>
+        <c:crossAx val="40462582"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3125,11 +3125,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="973665"/>
-        <c:axId val="68502039"/>
+        <c:axId val="98309437"/>
+        <c:axId val="25782867"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="973665"/>
+        <c:axId val="98309437"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3161,7 +3161,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68502039"/>
+        <c:crossAx val="25782867"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3169,7 +3169,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68502039"/>
+        <c:axId val="25782867"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3208,7 +3208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973665"/>
+        <c:crossAx val="98309437"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3719,7 +3719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
         <v>38</v>
       </c>
@@ -8426,10 +8426,10 @@
         <v>84</v>
       </c>
       <c r="L19" s="42" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="M19" s="42" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="N19" s="42" t="n">
         <v>96</v>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="P19" s="30" t="n">
         <f aca="false">AVERAGE(D19:O19)</f>
-        <v>85.8333333333333</v>
+        <v>84.4166666666667</v>
       </c>
       <c r="Q19" s="27" t="n">
         <f aca="false">O25</f>
@@ -8940,12 +8940,12 @@
       <c r="G32" s="24"/>
       <c r="H32" s="30" t="n">
         <f aca="false">AVERAGE(J19:L19)</f>
-        <v>84.6666666666667</v>
+        <v>82.3333333333333</v>
       </c>
       <c r="I32" s="30"/>
       <c r="J32" s="30" t="n">
         <f aca="false">AVERAGE(M19:O19)</f>
-        <v>95</v>
+        <v>91.6666666666667</v>
       </c>
       <c r="K32" s="30"/>
       <c r="L32" s="24" t="str">

--- a/Indicadores/Indicadores-modelo.xlsx
+++ b/Indicadores/Indicadores-modelo.xlsx
@@ -1795,11 +1795,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="8375249"/>
-        <c:axId val="97635148"/>
+        <c:axId val="66008744"/>
+        <c:axId val="1455592"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8375249"/>
+        <c:axId val="66008744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1831,7 +1831,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97635148"/>
+        <c:crossAx val="1455592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1839,7 +1839,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97635148"/>
+        <c:axId val="1455592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1878,7 +1878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8375249"/>
+        <c:crossAx val="66008744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2460,11 +2460,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="40462582"/>
-        <c:axId val="30770336"/>
+        <c:axId val="97985819"/>
+        <c:axId val="6671817"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40462582"/>
+        <c:axId val="97985819"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2496,7 +2496,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30770336"/>
+        <c:crossAx val="6671817"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2504,7 +2504,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30770336"/>
+        <c:axId val="6671817"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2543,7 +2543,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40462582"/>
+        <c:crossAx val="97985819"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3125,11 +3125,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="98309437"/>
-        <c:axId val="25782867"/>
+        <c:axId val="93209250"/>
+        <c:axId val="40671384"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98309437"/>
+        <c:axId val="93209250"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3161,7 +3161,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25782867"/>
+        <c:crossAx val="40671384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3169,7 +3169,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25782867"/>
+        <c:axId val="40671384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3208,7 +3208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98309437"/>
+        <c:crossAx val="93209250"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7642,13 +7642,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 12." errorStyle="stop" errorTitle="Número inválido" operator="between" prompt="Número do indicador, como na aba Fichas." promptTitle="Indicador" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D7:D21" type="whole">
+      <formula1>1</formula1>
+      <formula2>12</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C7:C21 J7:J21" type="date">
       <formula1>36526</formula1>
       <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 12." errorStyle="stop" errorTitle="Número inválido" operator="between" prompt="Número do indicador, como na aba Fichas." promptTitle="Indicador" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D7:D21" type="whole">
-      <formula1>1</formula1>
-      <formula2>12</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento ou Concluída" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K7:K21" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída"</formula1>
@@ -8432,14 +8432,14 @@
         <v>84</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O19" s="42" t="n">
         <v>95</v>
       </c>
       <c r="P19" s="30" t="n">
         <f aca="false">AVERAGE(D19:O19)</f>
-        <v>84.4166666666667</v>
+        <v>84.25</v>
       </c>
       <c r="Q19" s="27" t="n">
         <f aca="false">O25</f>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="N25" s="26" t="n">
         <f aca="false">IF(IF($Q12="Maior é melhor",N19&gt;=$O12,N19&lt;=$O12),0,N(M25)+1)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O25" s="26" t="n">
         <f aca="false">IF(IF($Q12="Maior é melhor",O19&gt;=$O12,O19&lt;=$O12),0,N(N25)+1)</f>
@@ -8945,7 +8945,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30" t="n">
         <f aca="false">AVERAGE(M19:O19)</f>
-        <v>91.6666666666667</v>
+        <v>91</v>
       </c>
       <c r="K32" s="30"/>
       <c r="L32" s="24" t="str">
